--- a/data/excel/08-hsinchu-city.xlsx
+++ b/data/excel/08-hsinchu-city.xlsx
@@ -872,7 +872,6 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1273,8 +1272,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -1297,6 +1302,222 @@
           <t>note</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>東區</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>新竹火車站</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>東區</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>東門市場</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>東區</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>城隍廟商圈</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>東區</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>經國路</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>北區</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>科學園區周邊</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>北區</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>竹蓮市場</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>北區</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>西大路</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>北區</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>北門街</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>香山區</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>南寮漁港</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>香山區</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>香山濕地</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>香山區</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>中華路</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>香山區</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>牛埔路</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
